--- a/graphing/coefficients_regression_EonG.xlsx
+++ b/graphing/coefficients_regression_EonG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repo\2024_within_fam_rge\graphing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CC8121-DE0F-4254-81A7-2DFC98D36282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9FC987-0034-4CA1-BEF1-A1BBB9674DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12660" windowHeight="16010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -77,115 +77,115 @@
     <t>population</t>
   </si>
   <si>
-    <t>-0.097*</t>
-  </si>
-  <si>
-    <t>-0.121 ~ -0.073</t>
-  </si>
-  <si>
-    <t>-0.051*</t>
-  </si>
-  <si>
-    <t>-0.075 ~ -0.028</t>
-  </si>
-  <si>
-    <t>0.111*</t>
-  </si>
-  <si>
-    <t>0.088 ~ 0.133</t>
-  </si>
-  <si>
-    <t>-0.069*</t>
-  </si>
-  <si>
-    <t>-0.093 ~ -0.046</t>
-  </si>
-  <si>
     <t>-0.093*</t>
   </si>
   <si>
-    <t>-0.174 ~ -0.011</t>
-  </si>
-  <si>
-    <t>-0.095*</t>
-  </si>
-  <si>
-    <t>-0.189 ~ -0.000</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>-0.070 ~ 0.100</t>
-  </si>
-  <si>
-    <t>-0.052 ~ 0.145</t>
-  </si>
-  <si>
-    <t>-0.170 ~ -0.019</t>
-  </si>
-  <si>
-    <t>-0.045</t>
-  </si>
-  <si>
-    <t>-0.112 ~ 0.022</t>
-  </si>
-  <si>
-    <t>0.207*</t>
-  </si>
-  <si>
-    <t>0.140 ~ 0.274</t>
-  </si>
-  <si>
-    <t>-0.046</t>
-  </si>
-  <si>
-    <t>-0.115 ~ 0.023</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>-0.002 ~ 0.171</t>
-  </si>
-  <si>
-    <t>0.102*</t>
-  </si>
-  <si>
-    <t>0.010 ~ 0.194</t>
-  </si>
-  <si>
-    <t>0.116 ~ 0.249</t>
-  </si>
-  <si>
-    <t>0.149*</t>
-  </si>
-  <si>
-    <t>0.182*</t>
-  </si>
-  <si>
-    <t>0.085 ~ 0.213</t>
-  </si>
-  <si>
-    <t>0.082 ~ 0.127</t>
-  </si>
-  <si>
-    <t>0.099 ~ 0.146</t>
-  </si>
-  <si>
-    <t>0.122*</t>
-  </si>
-  <si>
-    <t>0.105*</t>
-  </si>
-  <si>
     <t>PGS → SUB</t>
   </si>
   <si>
     <t>PGS → ASB</t>
+  </si>
+  <si>
+    <t>-0.091*</t>
+  </si>
+  <si>
+    <t>-0.172 ~ -0.010</t>
+  </si>
+  <si>
+    <t>-0.096*</t>
+  </si>
+  <si>
+    <t>-0.184 ~ -0.008</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>-0.072 ~ 0.087</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>-0.041 ~ 0.142</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>-0.006 ~ 0.154</t>
+  </si>
+  <si>
+    <t>0.089*</t>
+  </si>
+  <si>
+    <t>0.003 ~ 0.174</t>
+  </si>
+  <si>
+    <t>-0.171 ~ -0.020</t>
+  </si>
+  <si>
+    <t>-0.044</t>
+  </si>
+  <si>
+    <t>-0.106 ~ 0.018</t>
+  </si>
+  <si>
+    <t>0.193*</t>
+  </si>
+  <si>
+    <t>0.130 ~ 0.256</t>
+  </si>
+  <si>
+    <t>-0.051</t>
+  </si>
+  <si>
+    <t>-0.117 ~ 0.014</t>
+  </si>
+  <si>
+    <t>0.183*</t>
+  </si>
+  <si>
+    <t>0.121 ~ 0.245</t>
+  </si>
+  <si>
+    <t>0.151*</t>
+  </si>
+  <si>
+    <t>0.090 ~ 0.213</t>
+  </si>
+  <si>
+    <t>-0.116 ~ -0.070</t>
+  </si>
+  <si>
+    <t>-0.049*</t>
+  </si>
+  <si>
+    <t>-0.071 ~ -0.027</t>
+  </si>
+  <si>
+    <t>0.113*</t>
+  </si>
+  <si>
+    <t>0.092 ~ 0.134</t>
+  </si>
+  <si>
+    <t>-0.070*</t>
+  </si>
+  <si>
+    <t>-0.093 ~ -0.048</t>
+  </si>
+  <si>
+    <t>0.104*</t>
+  </si>
+  <si>
+    <t>0.083 ~ 0.125</t>
+  </si>
+  <si>
+    <t>0.119*</t>
+  </si>
+  <si>
+    <t>0.097 ~ 0.140</t>
   </si>
 </sst>
 </file>
@@ -542,10 +542,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -556,10 +556,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -570,10 +570,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -584,38 +584,38 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -626,7 +626,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>26</v>
@@ -676,30 +676,30 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -713,7 +713,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -724,10 +724,10 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -738,10 +738,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -752,38 +752,38 @@
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
